--- a/data/trans_camb/Hacinamiento_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 26,81</t>
+          <t>-0,24; 25,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 22,08</t>
+          <t>1,05; 21,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 4,13</t>
+          <t>-7,37; 4,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 23,71</t>
+          <t>4,3; 23,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 30,67</t>
+          <t>9,25; 29,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 13,61</t>
+          <t>0,5; 13,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 20,15</t>
+          <t>3,57; 18,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,54; 21,5</t>
+          <t>7,9; 21,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 7,3</t>
+          <t>-1,58; 6,95</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,85; 1213,0</t>
+          <t>-33,77; 1409,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 1015,59</t>
+          <t>-13,59; 1275,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>-87,43; 432,06</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,36; 1384,71</t>
+          <t>53,84; 1369,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>96,64; 1650,24</t>
+          <t>132,61; 1718,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-43,31; 530,02</t>
+          <t>-47,98; 608,66</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 5,63</t>
+          <t>-8,22; 6,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 16,3</t>
+          <t>-0,52; 16,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 1,34</t>
+          <t>-10,19; 1,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 7,86</t>
+          <t>-9,74; 7,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 5,22</t>
+          <t>-11,96; 4,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 8,76</t>
+          <t>-8,82; 8,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 4,75</t>
+          <t>-6,69; 5,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 7,66</t>
+          <t>-3,53; 7,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 3,0</t>
+          <t>-7,16; 3,4</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 167,28</t>
+          <t>-78,78; 210,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 407,13</t>
+          <t>-9,28; 414,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-90,75; 44,65</t>
+          <t>-87,33; 45,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,92; 112,78</t>
+          <t>-65,44; 114,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,32; 87,4</t>
+          <t>-74,37; 76,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,28; 143,88</t>
+          <t>-54,91; 127,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,64; 73,5</t>
+          <t>-56,47; 77,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,93; 115,63</t>
+          <t>-31,89; 127,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 44,79</t>
+          <t>-57,64; 54,83</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 7,17</t>
+          <t>-8,02; 6,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 3,32</t>
+          <t>-10,09; 3,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 20,02</t>
+          <t>1,59; 20,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 3,41</t>
+          <t>-10,88; 3,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 2,0</t>
+          <t>-11,81; 1,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 8,35</t>
+          <t>-7,98; 8,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 2,68</t>
+          <t>-7,63; 2,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 0,64</t>
+          <t>-9,16; 0,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 10,65</t>
+          <t>-1,52; 10,57</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,9; 308,2</t>
+          <t>-85,93; 310,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-95,73; 176,59</t>
+          <t>-100,0; 153,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 548,11</t>
+          <t>-0,57; 633,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-83,44; 86,2</t>
+          <t>-86,99; 115,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,34; 67,58</t>
+          <t>-88,69; 49,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,33; 147,35</t>
+          <t>-62,27; 162,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-74,07; 58,53</t>
+          <t>-71,94; 57,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,95; 23,35</t>
+          <t>-82,84; 23,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 191,88</t>
+          <t>-16,46; 195,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 6,64</t>
+          <t>-8,45; 7,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 20,69</t>
+          <t>0,31; 21,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 4,25</t>
+          <t>-9,24; 4,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 12,54</t>
+          <t>-4,44; 14,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 16,32</t>
+          <t>-2,29; 17,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 7,05</t>
+          <t>-8,2; 6,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 7,37</t>
+          <t>-4,94; 7,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 14,97</t>
+          <t>0,81; 15,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 3,42</t>
+          <t>-6,92; 3,13</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 247,1</t>
+          <t>-84,97; 419,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 524,2</t>
+          <t>-9,45; 601,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-93,5; 216,91</t>
+          <t>-92,73; 204,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,87; 455,27</t>
+          <t>-58,22; 477,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,52; 567,08</t>
+          <t>-34,47; 511,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 277,08</t>
+          <t>-100,0; 295,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-57,84; 164,31</t>
+          <t>-57,13; 172,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,05; 335,73</t>
+          <t>5,5; 364,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,62; 87,96</t>
+          <t>-77,45; 95,11</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 16,16</t>
+          <t>-29,38; 15,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-41,76; 9,35</t>
+          <t>-35,4; 9,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-40,9; 1,33</t>
+          <t>-39,69; 1,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 25,92</t>
+          <t>-9,34; 26,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 7,98</t>
+          <t>-23,28; 8,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 7,98</t>
+          <t>-19,02; 7,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 18,42</t>
+          <t>-10,37; 17,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 7,01</t>
+          <t>-17,92; 6,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 1,25</t>
+          <t>-22,83; 1,95</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-66,86; 726,88</t>
+          <t>-62,52; 487,36</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-81,44; —</t>
+          <t>-85,08; —</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 4,84</t>
+          <t>-9,01; 4,21</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 4,26</t>
+          <t>-10,61; 3,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 4,15</t>
+          <t>-10,04; 3,77</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 10,44</t>
+          <t>-1,02; 11,63</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 0,0</t>
+          <t>-5,85; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,54; 23,96</t>
+          <t>5,51; 24,43</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 5,25</t>
+          <t>-3,98; 5,72</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 1,22</t>
+          <t>-6,25; 1,69</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,28; 13,19</t>
+          <t>1,07; 12,4</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-93,0; 514,17</t>
+          <t>-100,0; 368,06</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-78,61; 482,17</t>
+          <t>-77,53; 312,09</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,14 +1903,14 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 713,84</t>
+          <t>-6,85; 980,43</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,98; 15,6</t>
+          <t>1,26; 14,98</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 0,23</t>
+          <t>-9,36; 0,23</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 10,56</t>
+          <t>-2,37; 10,93</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 9,86</t>
+          <t>-4,62; 9,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 1,46</t>
+          <t>-10,28; 0,86</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 10,79</t>
+          <t>-3,19; 10,92</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,43; 10,0</t>
+          <t>0,39; 10,21</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,98; -0,64</t>
+          <t>-8,1; -0,9</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 8,59</t>
+          <t>-0,92; 8,28</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>17,01; 360,43</t>
+          <t>7,91; 295,93</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-87,21; 9,3</t>
+          <t>-85,73; 21,4</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 221,86</t>
+          <t>-29,68; 206,98</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 171,2</t>
+          <t>-36,5; 171,4</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-79,62; 31,17</t>
+          <t>-80,4; 19,27</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 170,38</t>
+          <t>-25,82; 189,09</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,05; 157,37</t>
+          <t>1,39; 163,24</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-75,07; -8,1</t>
+          <t>-76,49; -11,09</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 133,5</t>
+          <t>-11,74; 130,64</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,17; 12,96</t>
+          <t>1,34; 13,18</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 9,04</t>
+          <t>-1,61; 8,64</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 1,43</t>
+          <t>-7,17; 1,12</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 0,82</t>
+          <t>-11,44; 0,44</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-15,8; -4,34</t>
+          <t>-15,71; -4,44</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-17,5; -6,13</t>
+          <t>-17,29; -6,27</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 5,09</t>
+          <t>-3,83; 4,99</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 0,48</t>
+          <t>-7,02; 0,41</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,61; -3,85</t>
+          <t>-10,65; -3,57</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 563,11</t>
+          <t>0,31; 619,09</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 456,53</t>
+          <t>-30,56; 441,76</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-88,88; 141,31</t>
+          <t>-89,53; 94,22</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-71,75; 14,79</t>
+          <t>-70,96; 12,64</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-92,55; -46,85</t>
+          <t>-92,46; -45,67</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-98,34; -67,97</t>
+          <t>-100,0; -69,81</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-33,38; 83,65</t>
+          <t>-35,17; 81,46</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-64,6; 11,2</t>
+          <t>-63,07; 8,9</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-92,19; -57,85</t>
+          <t>-92,17; -55,31</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,41</t>
+          <t>0,75; 6,63</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,66</t>
+          <t>-1,0; 4,65</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,77</t>
+          <t>-3,05; 2,02</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 4,07</t>
+          <t>-1,63; 4,02</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1,15</t>
+          <t>-4,03; 1,12</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,01</t>
+          <t>-2,51; 2,77</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,26</t>
+          <t>0,36; 4,44</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,02</t>
+          <t>-1,62; 2,07</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,73</t>
+          <t>-1,89; 1,61</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>3,02; 118,21</t>
+          <t>8,41; 121,93</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 85,52</t>
+          <t>-13,27; 86,89</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 33,79</t>
+          <t>-38,75; 40,44</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 58,71</t>
+          <t>-17,65; 61,61</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-41,85; 18,43</t>
+          <t>-43,07; 18,13</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 44,99</t>
+          <t>-26,87; 42,87</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4,12; 67,99</t>
+          <t>4,03; 71,64</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 33,18</t>
+          <t>-20,48; 31,94</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 26,33</t>
+          <t>-22,89; 25,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 25,02</t>
+          <t>-1,5; 23,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 21,97</t>
+          <t>0,49; 23,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 4,83</t>
+          <t>-7,44; 4,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 23,74</t>
+          <t>4,65; 25,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,25; 29,09</t>
+          <t>10,13; 29,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 13,75</t>
+          <t>0,95; 13,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 18,68</t>
+          <t>3,72; 19,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 21,74</t>
+          <t>7,73; 21,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 6,95</t>
+          <t>-1,49; 7,28</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,77; 1409,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 1275,17</t>
+          <t>-13,1; 1261,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-87,43; 432,06</t>
+          <t>-89,0; 360,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,84; 1369,19</t>
+          <t>52,75; 1529,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>132,61; 1718,92</t>
+          <t>119,17; 1504,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,98; 608,66</t>
+          <t>-47,86; 477,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 6,87</t>
+          <t>-8,02; 7,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 16,26</t>
+          <t>-1,29; 16,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 1,95</t>
+          <t>-10,52; 1,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 7,56</t>
+          <t>-10,14; 7,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 4,85</t>
+          <t>-10,82; 4,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 8,44</t>
+          <t>-8,33; 7,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 5,01</t>
+          <t>-6,67; 4,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 7,85</t>
+          <t>-4,0; 7,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 3,4</t>
+          <t>-7,28; 3,52</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-78,78; 210,53</t>
+          <t>-77,88; 196,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 414,18</t>
+          <t>-18,67; 415,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-87,33; 45,95</t>
+          <t>-88,37; 58,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,44; 114,74</t>
+          <t>-65,46; 112,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,37; 76,68</t>
+          <t>-67,76; 83,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,91; 127,85</t>
+          <t>-53,95; 116,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-56,47; 77,78</t>
+          <t>-55,56; 72,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 127,29</t>
+          <t>-33,27; 114,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-57,64; 54,83</t>
+          <t>-58,53; 52,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 6,93</t>
+          <t>-7,9; 6,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 3,09</t>
+          <t>-9,23; 3,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 20,64</t>
+          <t>1,33; 19,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 3,8</t>
+          <t>-10,94; 4,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 1,41</t>
+          <t>-11,05; 3,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 8,41</t>
+          <t>-8,27; 8,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 2,79</t>
+          <t>-7,87; 2,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 0,99</t>
+          <t>-9,29; 0,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 10,57</t>
+          <t>-1,57; 10,83</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,93; 310,44</t>
+          <t>-82,53; 228,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 153,33</t>
+          <t>-100,0; 162,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 633,39</t>
+          <t>5,35; 601,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-86,99; 115,79</t>
+          <t>-86,64; 101,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,69; 49,11</t>
+          <t>-87,58; 89,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,27; 162,28</t>
+          <t>-62,68; 168,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,94; 57,92</t>
+          <t>-76,99; 44,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,84; 23,59</t>
+          <t>-81,45; 26,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 195,15</t>
+          <t>-16,86; 207,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 7,4</t>
+          <t>-9,3; 6,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 21,21</t>
+          <t>0,55; 21,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 4,35</t>
+          <t>-10,05; 4,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 14,37</t>
+          <t>-5,09; 12,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 17,1</t>
+          <t>-2,19; 16,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 6,6</t>
+          <t>-8,59; 6,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 7,39</t>
+          <t>-4,48; 7,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 15,09</t>
+          <t>1,08; 15,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 3,13</t>
+          <t>-7,68; 2,97</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,97; 419,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 601,48</t>
+          <t>-9,14; 641,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-92,73; 204,05</t>
+          <t>-92,92; 211,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,22; 477,69</t>
+          <t>-55,7; 378,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 511,52</t>
+          <t>-33,37; 531,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 295,48</t>
+          <t>-100,0; 237,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-57,13; 172,49</t>
+          <t>-54,5; 226,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,5; 364,68</t>
+          <t>4,72; 353,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,45; 95,11</t>
+          <t>-81,3; 83,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-29,38; 15,88</t>
+          <t>-31,99; 15,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 9,55</t>
+          <t>-35,83; 8,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 1,34</t>
+          <t>-39,99; 1,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 26,32</t>
+          <t>-7,81; 25,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 8,19</t>
+          <t>-21,2; 7,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 7,85</t>
+          <t>-21,25; 7,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 17,56</t>
+          <t>-11,66; 17,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 6,73</t>
+          <t>-19,14; 6,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 1,95</t>
+          <t>-23,64; 1,43</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-62,52; 487,36</t>
+          <t>-67,39; 562,53</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-85,08; —</t>
+          <t>-85,19; 326,42</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 4,21</t>
+          <t>-10,18; 4,63</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 3,58</t>
+          <t>-10,43; 4,23</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 3,77</t>
+          <t>-9,3; 3,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 11,63</t>
+          <t>-1,1; 10,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 0,0</t>
+          <t>-6,36; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,51; 24,43</t>
+          <t>5,39; 24,34</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 5,72</t>
+          <t>-3,85; 5,46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,69</t>
+          <t>-6,28; 0,98</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,07; 12,4</t>
+          <t>0,25; 13,74</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 368,06</t>
+          <t>-100,0; 347,01</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-77,53; 312,09</t>
+          <t>-82,42; 397,39</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 447,78</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 980,43</t>
+          <t>-20,84; 694,6</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,26; 14,98</t>
+          <t>1,25; 15,66</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 0,23</t>
+          <t>-9,73; 0,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 10,93</t>
+          <t>-2,5; 10,14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 9,4</t>
+          <t>-4,21; 8,83</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 0,86</t>
+          <t>-10,34; 0,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 10,92</t>
+          <t>-2,58; 11,15</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 10,21</t>
+          <t>0,68; 10,2</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,1; -0,9</t>
+          <t>-8,12; -0,55</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 8,28</t>
+          <t>-0,7; 8,34</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,91; 295,93</t>
+          <t>7,53; 353,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-85,73; 21,4</t>
+          <t>-87,66; 40,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 206,98</t>
+          <t>-27,09; 220,35</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,5; 171,4</t>
+          <t>-36,24; 134,25</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-80,4; 19,27</t>
+          <t>-80,23; 23,01</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 189,09</t>
+          <t>-26,46; 177,4</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,39; 163,24</t>
+          <t>6,0; 165,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-76,49; -11,09</t>
+          <t>-75,01; -5,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 130,64</t>
+          <t>-8,47; 131,25</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,34; 13,18</t>
+          <t>1,72; 13,44</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 8,64</t>
+          <t>-1,63; 8,38</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 1,12</t>
+          <t>-6,81; 1,7</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 0,44</t>
+          <t>-11,0; 1,06</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-15,71; -4,44</t>
+          <t>-15,39; -3,33</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-17,29; -6,27</t>
+          <t>-17,27; -5,58</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 4,99</t>
+          <t>-3,8; 5,02</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 0,41</t>
+          <t>-7,01; 0,52</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,65; -3,57</t>
+          <t>-10,55; -3,58</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0,31; 619,09</t>
+          <t>14,24; 797,0</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 441,76</t>
+          <t>-28,3; 427,25</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-89,53; 94,22</t>
+          <t>-87,93; 152,44</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-70,96; 12,64</t>
+          <t>-70,92; 15,31</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-92,46; -45,67</t>
+          <t>-91,91; -35,9</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -69,81</t>
+          <t>-98,22; -67,02</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-35,17; 81,46</t>
+          <t>-35,41; 82,46</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-63,07; 8,9</t>
+          <t>-62,55; 13,12</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-92,17; -55,31</t>
+          <t>-91,49; -53,36</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,63</t>
+          <t>0,79; 6,62</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,65</t>
+          <t>-0,64; 4,84</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,02</t>
+          <t>-3,15; 1,68</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 4,02</t>
+          <t>-1,56; 3,88</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,12</t>
+          <t>-4,03; 1,21</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,77</t>
+          <t>-2,49; 3,16</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,44</t>
+          <t>0,35; 4,35</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,07</t>
+          <t>-1,8; 1,88</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,61</t>
+          <t>-1,84; 1,72</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>8,41; 121,93</t>
+          <t>9,1; 128,79</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 86,89</t>
+          <t>-10,37; 95,68</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 40,44</t>
+          <t>-39,24; 30,35</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 61,61</t>
+          <t>-17,05; 56,53</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 18,13</t>
+          <t>-42,73; 18,61</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 42,87</t>
+          <t>-27,34; 46,24</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4,03; 71,64</t>
+          <t>3,38; 67,98</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 31,94</t>
+          <t>-22,45; 28,57</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 25,69</t>
+          <t>-22,85; 27,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,06</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18,23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,23</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>10,3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>10,06</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,06</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,23</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,07</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,58</t>
+          <t>2,37</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 23,65</t>
+          <t>4,08; 23,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 23,09</t>
+          <t>9,63; 30,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 4,68</t>
+          <t>0,61; 12,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 25,28</t>
+          <t>-0,52; 26,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 29,43</t>
+          <t>1,2; 22,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 13,73</t>
+          <t>-6,97; 4,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 19,65</t>
+          <t>4,2; 20,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 21,87</t>
+          <t>7,54; 21,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 7,28</t>
+          <t>-1,49; 6,72</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>901,36%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1362,63%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>391,17%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>208,87%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>203,88%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-23,82%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>901,36%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1362,63%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>453,48%</t>
+          <t>-15,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>77,19%</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 1261,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,0; 360,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>-43,85; 1213,0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>-13,55; 1015,59</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,75; 1529,02</t>
+          <t>48,36; 1384,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>119,17; 1504,02</t>
+          <t>96,64; 1650,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,86; 477,18</t>
+          <t>-45,01; 525,76</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,09</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,63</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,14</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7,42</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,71</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,63</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>-2,49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-0,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 7,14</t>
+          <t>-9,17; 7,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 16,25</t>
+          <t>-10,97; 5,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 1,49</t>
+          <t>-8,17; 9,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 7,69</t>
+          <t>-8,2; 5,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 4,91</t>
+          <t>-0,65; 16,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 7,77</t>
+          <t>-10,05; 2,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 4,66</t>
+          <t>-6,84; 4,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 7,28</t>
+          <t>-3,97; 7,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 3,52</t>
+          <t>-5,94; 4,16</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-9,8%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-23,55%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-15,16%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>98,58%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-49,25%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-9,8%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-23,55%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>-33,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,48%</t>
+          <t>-8,95%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,88; 196,61</t>
+          <t>-64,92; 112,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 415,22</t>
+          <t>-68,32; 87,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,37; 58,91</t>
+          <t>-50,84; 148,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,46; 112,95</t>
+          <t>-78,25; 167,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,76; 83,36</t>
+          <t>-13,28; 407,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,95; 116,2</t>
+          <t>-85,74; 86,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,56; 72,59</t>
+          <t>-58,64; 73,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 114,32</t>
+          <t>-32,93; 115,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,53; 52,26</t>
+          <t>-49,21; 64,75</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,02</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,65</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,36</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-3,03</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10,12</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,02</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,65</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>9,64</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>4,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 6,06</t>
+          <t>-10,43; 3,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 3,83</t>
+          <t>-11,58; 2,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 19,04</t>
+          <t>-7,93; 8,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 4,17</t>
+          <t>-8,22; 7,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 3,27</t>
+          <t>-10,09; 3,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 8,53</t>
+          <t>0,79; 19,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 2,28</t>
+          <t>-7,76; 2,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 0,76</t>
+          <t>-8,73; 0,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 10,83</t>
+          <t>-1,41; 10,43</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-43,8%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-50,67%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-3,95%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-17,78%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-44,74%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>149,3%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-43,8%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-50,67%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-1,81%</t>
+          <t>142,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>56,37%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,53; 228,91</t>
+          <t>-83,44; 86,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 162,62</t>
+          <t>-86,34; 67,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,35; 601,93</t>
+          <t>-65,05; 142,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-86,64; 101,67</t>
+          <t>-82,9; 308,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,58; 89,09</t>
+          <t>-95,73; 176,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,68; 168,37</t>
+          <t>-4,65; 540,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,99; 44,03</t>
+          <t>-74,07; 58,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,45; 26,85</t>
+          <t>-80,95; 23,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 207,36</t>
+          <t>-15,57; 188,0</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,45</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6,15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,42</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,64</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>9,61</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,8</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,45</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,15</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,16</t>
+          <t>-2,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 6,39</t>
+          <t>-4,24; 12,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 21,38</t>
+          <t>-3,08; 16,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 4,39</t>
+          <t>-8,5; 7,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 12,95</t>
+          <t>-8,77; 6,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 16,46</t>
+          <t>-0,98; 20,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 6,33</t>
+          <t>-10,65; 1,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 7,14</t>
+          <t>-5,14; 7,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 15,07</t>
+          <t>0,91; 14,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 2,97</t>
+          <t>-7,45; 3,01</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>53,17%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-21,8%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-24,04%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>140,58%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-40,89%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>53,17%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>94,76%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-24,46%</t>
+          <t>-52,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-32,4%</t>
+          <t>-37,18%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-56,87; 455,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 641,38</t>
+          <t>-41,52; 567,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-92,92; 211,75</t>
+          <t>-100,0; 287,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,7; 378,42</t>
+          <t>-100,0; 247,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,37; 531,85</t>
+          <t>-24,32; 524,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 237,4</t>
+          <t>-93,89; 107,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-54,5; 226,3</t>
+          <t>-57,84; 164,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,72; 353,76</t>
+          <t>3,05; 335,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-81,3; 83,01</t>
+          <t>-79,97; 79,62</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10,48</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-4,54</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-3,23</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-5,95</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-13,5</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10,48</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,42</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>-13,33</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-7,38</t>
+          <t>-8,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-31,99; 15,48</t>
+          <t>-8,24; 25,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-35,83; 8,93</t>
+          <t>-22,82; 7,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-39,99; 1,34</t>
+          <t>-24,04; 3,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 25,93</t>
+          <t>-29,42; 16,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 7,75</t>
+          <t>-41,76; 9,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 7,82</t>
+          <t>-40,56; 1,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 17,34</t>
+          <t>-11,27; 18,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 6,94</t>
+          <t>-17,14; 7,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 1,43</t>
+          <t>-23,14; -0,4</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>169,44%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-6,77%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-73,39%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-21,76%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-40,08%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-90,97%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>169,44%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-6,77%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-36,15%</t>
+          <t>-89,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-72,83%</t>
+          <t>-84,37%</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-67,39; 562,53</t>
+          <t>-66,86; 726,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-85,19; 326,42</t>
+          <t>-81,44; —</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>3,32</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-1,27</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>12,98</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-2,72</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-3,54</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-2,58</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3,32</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-1,27</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,85</t>
+          <t>-2,91</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,83</t>
+          <t>5,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 4,63</t>
+          <t>-1,08; 10,44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 4,23</t>
+          <t>-6,42; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 3,88</t>
+          <t>5,64; 24,01</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 10,43</t>
+          <t>-10,19; 4,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 0,0</t>
+          <t>-11,19; 4,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,39; 24,34</t>
+          <t>-10,62; 3,35</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 5,46</t>
+          <t>-3,7; 5,25</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 0,98</t>
+          <t>-5,97; 1,22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,25; 13,74</t>
+          <t>0,03; 12,43</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>261,25%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1021,35%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-45,56%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-59,14%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-43,24%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>261,25%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1011,4%</t>
+          <t>-48,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>167,12%</t>
+          <t>154,64%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 347,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
+          <t>-93,42; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-78,61; 482,17</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-82,42; 397,39</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 447,78</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-20,84; 694,6</t>
+          <t>-17,81; 632,56</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2,42</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-4,31</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4,57</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>8,29</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-4,34</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3,83</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2,42</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-4,31</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,09</t>
+          <t>4,24</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>4,47</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,25; 15,66</t>
+          <t>-4,08; 9,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 0,71</t>
+          <t>-9,93; 1,46</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 10,14</t>
+          <t>-2,95; 11,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 8,83</t>
+          <t>1,98; 15,6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 0,83</t>
+          <t>-9,09; 0,23</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 11,15</t>
+          <t>-1,98; 11,29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,68; 10,2</t>
+          <t>0,43; 10,0</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,12; -0,55</t>
+          <t>-7,98; -0,64</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 8,34</t>
+          <t>-0,34; 9,02</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>26,37%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-47,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>49,77%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>108,74%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-56,9%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>50,19%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>26,37%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-47,0%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,53; 353,96</t>
+          <t>-34,42; 171,2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-87,66; 40,81</t>
+          <t>-79,62; 31,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 220,35</t>
+          <t>-25,39; 177,69</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 134,25</t>
+          <t>17,01; 360,43</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-80,23; 23,01</t>
+          <t>-87,21; 9,3</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 177,4</t>
+          <t>-22,43; 228,31</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,0; 165,34</t>
+          <t>2,05; 157,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-75,01; -5,31</t>
+          <t>-75,07; -8,1</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 131,25</t>
+          <t>-3,78; 144,68</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-5,01</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-9,28</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-11,12</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>7,26</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>3,58</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-2,08</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-5,01</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-9,28</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-11,01</t>
+          <t>-1,3</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-6,76</t>
+          <t>-6,45</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,72; 13,44</t>
+          <t>-11,89; 0,82</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 8,38</t>
+          <t>-15,8; -4,34</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 1,7</t>
+          <t>-17,54; -6,31</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 1,06</t>
+          <t>1,17; 12,96</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-15,39; -3,33</t>
+          <t>-1,34; 9,04</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-17,27; -5,58</t>
+          <t>-6,45; 2,6</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 5,02</t>
+          <t>-3,63; 5,09</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 0,52</t>
+          <t>-7,1; 0,48</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,55; -3,58</t>
+          <t>-10,44; -3,46</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-41,37%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-76,68%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-91,86%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>163,67%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>80,66%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-46,89%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-41,37%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-76,68%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-90,91%</t>
+          <t>-29,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-80,22%</t>
+          <t>-76,52%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>14,24; 797,0</t>
+          <t>-71,75; 14,79</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 427,25</t>
+          <t>-92,55; -46,85</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-87,93; 152,44</t>
+          <t>-98,65; -70,92</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-70,92; 15,31</t>
+          <t>-10,75; 563,11</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-91,91; -35,9</t>
+          <t>-27,78; 456,53</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-98,22; -67,02</t>
+          <t>-83,08; 198,41</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 82,46</t>
+          <t>-33,38; 83,65</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-62,55; 13,12</t>
+          <t>-64,6; 11,2</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-91,49; -53,36</t>
+          <t>-90,08; -50,89</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>1,19</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-0,12</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1,96</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,62</t>
+          <t>-1,78; 4,07</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,84</t>
+          <t>-3,93; 1,15</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,68</t>
+          <t>-2,67; 2,66</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,88</t>
+          <t>0,45; 6,41</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,21</t>
+          <t>-0,95; 4,66</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,16</t>
+          <t>-2,6; 2,2</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,35</t>
+          <t>0,3; 4,26</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,88</t>
+          <t>-1,49; 2,02</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,72</t>
+          <t>-1,8; 1,76</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>14,94%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-17,02%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-1,51%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>54,91%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>29,88%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-8,99%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-17,02%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>-3,06%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-1,92%</t>
+          <t>-1,87%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>9,1; 128,79</t>
+          <t>-20,85; 58,71</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 95,68</t>
+          <t>-41,85; 18,43</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 30,35</t>
+          <t>-29,43; 40,24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 56,53</t>
+          <t>3,02; 118,21</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-42,73; 18,61</t>
+          <t>-12,62; 85,52</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 46,24</t>
+          <t>-34,19; 42,61</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,38; 67,98</t>
+          <t>4,12; 67,99</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 28,57</t>
+          <t>-18,8; 33,18</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-22,85; 27,28</t>
+          <t>-22,53; 28,33</t>
         </is>
       </c>
     </row>
